--- a/main/StructureDefinition-Patient.xlsx
+++ b/main/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.1.0</t>
+    <t>2026.2.0-rc</t>
   </si>
   <si>
     <t>Name</t>

--- a/main/StructureDefinition-Patient.xlsx
+++ b/main/StructureDefinition-Patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05</t>
+    <t>2026-09-16</t>
   </si>
   <si>
     <t>Publisher</t>
